--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1310,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1375,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1501,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1566,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1875,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2062,11 @@
           <t>76.701.829-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2371,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2558,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2806,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3664,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3729,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3855,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4103,11 @@
           <t>76.271.360-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4534,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +4965,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5396,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5644,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5770,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5835,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5961,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6026,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6457,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6583,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6709,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +6957,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7022,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7270,11 @@
           <t>76.271.360-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7884,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8376,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8441,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8689,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8754,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9368,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9494,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9620,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9807,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9933,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +9998,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10795,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11104,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +11962,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12149,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12275,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12584,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12771,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12836,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13267,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13332,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13397,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13462,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13527,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13592,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +13901,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +13966,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14214,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14340,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14466,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14531,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14657,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14783,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14909,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15218,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15283,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15409,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15474,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15539,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15604,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15791,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15856,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15921,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +15986,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16051,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16177,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16242,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16429,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16555,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +16986,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17173,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17360,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17547,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17612,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +17799,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +17864,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +17929,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18360,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18425,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18612,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19165,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19474,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19600,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +19909,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +19974,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20222,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20348,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +20840,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21088,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21153,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21218,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21283,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21531,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21657,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +21844,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +21909,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22340,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22527,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +22653,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +22718,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +22844,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +22970,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23096,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M364"/>
+  <dimension ref="A1:M383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1953,7 +1953,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3130-1509-CM25</t>
+          <t>874750-85-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1011.86</v>
+        <v>1341.28</v>
       </c>
     </row>
     <row r="26">
@@ -2079,7 +2079,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057402-15322-CM25</t>
+          <t>3130-1509-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2119,28 +2119,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>84.609.600-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4529.17</v>
+        <v>1011.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057402-14726-CM25</t>
+          <t>1057402-15322-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2180,28 +2184,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2217.87</v>
+        <v>4529.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>874750-85-CM25</t>
+          <t>1057402-14726-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2221,17 +2229,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2256,7 +2264,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1341.28</v>
+        <v>2217.87</v>
       </c>
     </row>
     <row r="30">
@@ -3006,7 +3014,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1540-825-CM25</t>
+          <t>874750-130-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3026,17 +3034,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3061,13 +3069,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5216.37</v>
+        <v>1784.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>874750-130-CM25</t>
+          <t>874750-131-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3107,12 +3115,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3122,13 +3130,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1784.25</v>
+        <v>1290.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>874750-131-CM25</t>
+          <t>1540-825-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3148,17 +3156,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3168,12 +3176,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3183,7 +3191,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1290.63</v>
+        <v>5216.37</v>
       </c>
     </row>
     <row r="45">
@@ -3237,7 +3245,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3506,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1540-922-CM25</t>
+          <t>1540-923-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3534,22 +3546,26 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CEGAMED CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>99.593.170-2</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1822.2</v>
+        <v>1133.7</v>
       </c>
     </row>
     <row r="51">
@@ -3681,7 +3697,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1540-923-CM25</t>
+          <t>1540-922-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3721,32 +3737,28 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>CEGAMED CHILE S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.593.170-2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1133.7</v>
+        <v>1822.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3130-1831-CM25</t>
+          <t>3130-1825-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3786,12 +3798,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3801,7 +3813,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>739.39</v>
+        <v>920.12</v>
       </c>
     </row>
     <row r="55">
@@ -3872,7 +3884,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3130-1826-CM25</t>
+          <t>3130-1829-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3912,12 +3924,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3927,13 +3939,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1529.97</v>
+        <v>825.48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3130-1825-CM25</t>
+          <t>3130-1831-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3973,12 +3985,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3988,13 +4000,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>920.12</v>
+        <v>739.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3130-1829-CM25</t>
+          <t>3130-1826-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4034,12 +4046,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4049,7 +4061,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>825.48</v>
+        <v>1529.97</v>
       </c>
     </row>
     <row r="59">
@@ -4181,7 +4193,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1237328-109-CM25</t>
+          <t>1237328-111-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4221,12 +4233,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4236,13 +4248,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>20316.96</v>
+        <v>4111.22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1237328-111-CM25</t>
+          <t>1237328-109-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4282,12 +4294,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4297,7 +4309,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4111.22</v>
+        <v>20316.96</v>
       </c>
     </row>
     <row r="63">
@@ -4425,7 +4437,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3130-1980-CM25</t>
+          <t>1057402-23613-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4450,12 +4462,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4465,12 +4477,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>BIOHEIS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.532.722-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4480,13 +4492,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1825.21</v>
+        <v>772.3200000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3130-1981-CM25</t>
+          <t>3130-1980-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4526,32 +4538,28 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>924.62</v>
+        <v>1825.21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057402-23613-CM25</t>
+          <t>3130-1981-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4576,12 +4584,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4591,22 +4599,26 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>BIOHEIS SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.532.722-9</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>772.3200000000001</v>
+        <v>924.62</v>
       </c>
     </row>
     <row r="68">
@@ -5043,7 +5055,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3130-2155-CM25</t>
+          <t>1057402-24520-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5068,12 +5080,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5083,12 +5095,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Pulsar Medical</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5098,13 +5110,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>757.98</v>
+        <v>1505.75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1057402-24520-CM25</t>
+          <t>3130-2155-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5129,12 +5141,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5144,12 +5156,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Pulsar Medical</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5159,7 +5171,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1505.75</v>
+        <v>757.98</v>
       </c>
     </row>
     <row r="77">
@@ -5474,7 +5486,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1237328-217-CM25</t>
+          <t>1057402-25779-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5499,12 +5511,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5514,12 +5526,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>Pulsar Medical</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5529,13 +5541,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4478.14</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057402-25779-CM25</t>
+          <t>1237328-217-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5560,12 +5572,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5575,12 +5587,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Pulsar Medical</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5590,13 +5602,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1479.2</v>
+        <v>4478.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3130-2364-CM25</t>
+          <t>3130-2372-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5655,13 +5667,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3005.65</v>
+        <v>735.33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3130-2365-CM25</t>
+          <t>3130-2364-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5701,28 +5713,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>77.910.467-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1977.89</v>
+        <v>3005.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3130-2367-CM25</t>
+          <t>3130-2365-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5762,26 +5778,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1695.69</v>
+        <v>1977.89</v>
       </c>
     </row>
     <row r="87">
@@ -5913,7 +5925,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3130-2372-CM25</t>
+          <t>3130-2367-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5953,12 +5965,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5972,7 +5984,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>735.33</v>
+        <v>1695.69</v>
       </c>
     </row>
     <row r="90">
@@ -6104,7 +6116,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1237328-221-CM25</t>
+          <t>1237328-222-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6144,12 +6156,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6159,13 +6171,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>750.6</v>
+        <v>868.6900000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1237328-222-CM25</t>
+          <t>1237328-221-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6205,12 +6217,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6220,7 +6232,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>868.6900000000001</v>
+        <v>750.6</v>
       </c>
     </row>
     <row r="94">
@@ -6522,7 +6534,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6600,7 +6616,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057402-26767-CM25</t>
+          <t>1057402-26752-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6640,28 +6656,32 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>756.63</v>
+        <v>1043.64</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1057402-26752-CM25</t>
+          <t>1057402-26767-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6701,26 +6721,22 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1043.64</v>
+        <v>756.63</v>
       </c>
     </row>
     <row r="102">
@@ -6909,7 +6925,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1540-1888-CM25</t>
+          <t>1540-1887-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6929,7 +6945,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6949,12 +6965,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6968,13 +6984,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1351.1</v>
+        <v>1255.64</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1540-1887-CM25</t>
+          <t>1540-1888-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6994,7 +7010,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7014,12 +7030,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7033,7 +7049,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1255.64</v>
+        <v>1351.1</v>
       </c>
     </row>
     <row r="107">
@@ -7161,7 +7177,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1237328-387-CM25</t>
+          <t>1057402-27878-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7186,12 +7202,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7201,12 +7217,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7216,13 +7232,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4851.18</v>
+        <v>786.1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>874750-376-CM25</t>
+          <t>1057402-27876-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7242,17 +7258,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7262,32 +7278,28 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>MAYORDENT DENTAL LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.271.360-8</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>762.61</v>
+        <v>1023.72</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1057402-27878-CM25</t>
+          <t>1237328-387-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7312,12 +7324,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7327,12 +7339,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7342,13 +7354,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>786.1</v>
+        <v>4851.18</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1057402-27876-CM25</t>
+          <t>874750-376-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7368,17 +7380,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7388,22 +7400,26 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MAYORDENT DENTAL LIMITADA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>76.271.360-8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1023.72</v>
+        <v>762.61</v>
       </c>
     </row>
     <row r="113">
@@ -7470,7 +7486,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1237328-470-CM25</t>
+          <t>1237328-467-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7510,12 +7526,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7525,13 +7541,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1525.45</v>
+        <v>1640.44</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1237328-467-CM25</t>
+          <t>1237328-468-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7571,12 +7587,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7586,13 +7602,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1640.44</v>
+        <v>4842.1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1237328-468-CM25</t>
+          <t>1237328-470-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7647,7 +7663,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4842.1</v>
+        <v>1525.45</v>
       </c>
     </row>
     <row r="117">
@@ -7714,7 +7730,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1540-2123-CM25</t>
+          <t>1540-2126-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7754,28 +7770,32 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4815.1</v>
+        <v>974.87</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1540-2125-CM25</t>
+          <t>1540-2122-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7815,12 +7835,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7830,13 +7850,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7562.31</v>
+        <v>726.24</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1540-2126-CM25</t>
+          <t>1540-2124-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7876,32 +7896,28 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.020.266-5</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>974.87</v>
+        <v>864.9299999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1540-2124-CM25</t>
+          <t>1540-2123-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7941,12 +7957,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7956,13 +7972,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>864.9299999999999</v>
+        <v>4815.1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1540-2122-CM25</t>
+          <t>1540-2121-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8002,12 +8018,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -8017,13 +8033,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>726.24</v>
+        <v>831.78</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1540-2121-CM25</t>
+          <t>1540-2125-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8063,12 +8079,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -8078,7 +8094,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>831.78</v>
+        <v>7562.31</v>
       </c>
     </row>
     <row r="124">
@@ -8206,7 +8222,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>902977-24-CM25</t>
+          <t>874750-418-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8226,17 +8242,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8246,12 +8262,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8261,7 +8277,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>811.34</v>
+        <v>1009.72</v>
       </c>
     </row>
     <row r="127">
@@ -8458,7 +8474,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>874750-418-CM25</t>
+          <t>902977-24-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8478,17 +8494,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8498,12 +8514,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8513,7 +8529,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1009.72</v>
+        <v>811.34</v>
       </c>
     </row>
     <row r="131">
@@ -8893,7 +8909,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>874750-445-CM25</t>
+          <t>3130-2969-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8913,17 +8929,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8948,13 +8964,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2085.23</v>
+        <v>743.8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>874750-442-CM25</t>
+          <t>874750-445-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8994,12 +9010,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -9009,13 +9025,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1015.69</v>
+        <v>2085.23</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3130-2969-CM25</t>
+          <t>874750-442-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9035,17 +9051,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9055,12 +9071,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -9070,7 +9086,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>743.8</v>
+        <v>1015.69</v>
       </c>
     </row>
     <row r="140">
@@ -9137,7 +9153,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3130-4029-CM25</t>
+          <t>3130-4031-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9177,12 +9193,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>CEGASURGICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.705.621-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9192,13 +9208,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>765.4</v>
+        <v>2258.02</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3130-4031-CM25</t>
+          <t>3130-4029-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9238,12 +9254,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>CEGASURGICAL SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.705.621-4</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9253,7 +9269,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2258.02</v>
+        <v>765.4</v>
       </c>
     </row>
     <row r="143">
@@ -10320,7 +10336,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1237328-702-CM25</t>
+          <t>1237328-703-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10360,12 +10376,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10375,13 +10391,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1196.01</v>
+        <v>5510.8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3130-4447-CM25</t>
+          <t>1237328-702-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10406,12 +10422,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10421,12 +10437,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10436,13 +10452,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2449.78</v>
+        <v>1196.01</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1237328-705-CM25</t>
+          <t>3130-4447-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10467,12 +10483,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10482,12 +10498,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10497,13 +10513,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>5051.56</v>
+        <v>2449.78</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1237328-704-CM25</t>
+          <t>1237328-705-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10543,12 +10559,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10558,13 +10574,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1996.24</v>
+        <v>5051.56</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1237328-703-CM25</t>
+          <t>1237328-704-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10619,7 +10635,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5510.8</v>
+        <v>1996.24</v>
       </c>
     </row>
     <row r="165">
@@ -11182,7 +11198,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1057402-156-CM26</t>
+          <t>1057402-165-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11222,12 +11238,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11237,13 +11253,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2017.43</v>
+        <v>924.8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057402-165-CM26</t>
+          <t>1057402-156-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11283,12 +11299,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11298,13 +11314,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>924.8</v>
+        <v>2017.43</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1057402-44949-CM25</t>
+          <t>1057402-286-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11344,12 +11360,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11359,13 +11375,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>822.42</v>
+        <v>908.26</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1057402-213-CM26</t>
+          <t>1057402-242-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11405,12 +11421,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>MEDICINA TECNICA LTDA</t>
+          <t>Pulsar Medical</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>78.297.510-2</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11420,13 +11436,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1421.42</v>
+        <v>1834.19</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1057402-242-CM26</t>
+          <t>1057402-44949-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11466,12 +11482,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Pulsar Medical</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11481,13 +11497,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1834.19</v>
+        <v>822.42</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1057402-286-CM26</t>
+          <t>1057402-213-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11527,12 +11543,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>MEDICINA TECNICA LTDA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>78.297.510-2</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11542,7 +11558,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>908.26</v>
+        <v>1421.42</v>
       </c>
     </row>
     <row r="180">
@@ -11731,7 +11747,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3130-5203-CM26</t>
+          <t>1057402-611-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11756,12 +11772,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11771,12 +11787,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>DISTRIBUIDORA FASTMED  SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.994.349-8</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11786,13 +11802,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1637.06</v>
+        <v>1100.1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1057402-611-CM26</t>
+          <t>3130-5203-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11817,12 +11833,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11832,12 +11848,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA FASTMED  SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.994.349-8</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11847,7 +11863,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1100.1</v>
+        <v>1637.06</v>
       </c>
     </row>
     <row r="185">
@@ -12101,7 +12117,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1057402-1177-CM26</t>
+          <t>3130-5281-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12126,12 +12142,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12141,32 +12157,28 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.400-5</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>891.08</v>
+        <v>1423.79</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3130-5281-CM26</t>
+          <t>874750-27-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12186,17 +12198,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12206,28 +12218,32 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1423.79</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>874750-27-CM26</t>
+          <t>1057402-1177-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12247,17 +12263,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12267,12 +12283,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -12286,13 +12302,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>905.4400000000001</v>
+        <v>891.08</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1057402-1023-CM26</t>
+          <t>1057402-1110-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12332,12 +12348,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12347,13 +12363,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>843.3099999999999</v>
+        <v>923.76</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1057402-1110-CM26</t>
+          <t>1057402-1023-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12393,12 +12409,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12408,7 +12424,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>923.76</v>
+        <v>843.3099999999999</v>
       </c>
     </row>
     <row r="194">
@@ -13158,7 +13174,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3130-5423-CM26</t>
+          <t>1057402-2301-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13183,12 +13199,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13198,28 +13214,32 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1052.94</v>
+        <v>813.9299999999999</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1057402-2316-CM26</t>
+          <t>1057402-2304-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13259,12 +13279,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -13278,13 +13298,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>941.36</v>
+        <v>829.09</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1057402-2301-CM26</t>
+          <t>1057402-2316-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13324,12 +13344,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -13343,13 +13363,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>813.9299999999999</v>
+        <v>941.36</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1057402-2304-CM26</t>
+          <t>3130-5423-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13374,12 +13394,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13389,26 +13409,22 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.054.237-7</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>829.09</v>
+        <v>1052.94</v>
       </c>
     </row>
     <row r="210">
@@ -13544,7 +13560,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>874750-78-CM26</t>
+          <t>3130-5458-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13564,17 +13580,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13584,32 +13600,28 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>771.91</v>
+        <v>886.26</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3130-5458-CM26</t>
+          <t>874750-78-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13629,17 +13641,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13649,22 +13661,26 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>886.26</v>
+        <v>771.91</v>
       </c>
     </row>
     <row r="214">
@@ -13731,7 +13747,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>874750-80-CM26</t>
+          <t>874750-81-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13771,12 +13787,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13786,13 +13802,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1348.55</v>
+        <v>6731.23</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>874750-81-CM26</t>
+          <t>874750-80-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13832,12 +13848,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13847,7 +13863,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>6731.23</v>
+        <v>1348.55</v>
       </c>
     </row>
     <row r="217">
@@ -14044,7 +14060,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1057402-2470-CM26</t>
+          <t>855-35-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14069,12 +14085,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14099,13 +14115,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3295.21</v>
+        <v>4223.46</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>855-35-CM26</t>
+          <t>1057402-2470-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14130,12 +14146,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14160,13 +14176,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4223.46</v>
+        <v>3295.21</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1057402-2985-CM26</t>
+          <t>1237328-88-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14191,12 +14207,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14206,32 +14222,28 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1115.79</v>
+        <v>16669.09</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1237328-88-CM26</t>
+          <t>1057402-2985-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14256,12 +14268,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14271,28 +14283,32 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>16669.09</v>
+        <v>1115.79</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1540-695-CM26</t>
+          <t>1540-698-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14332,12 +14348,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -14351,7 +14367,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1337.2</v>
+        <v>785.98</v>
       </c>
     </row>
     <row r="225">
@@ -14418,7 +14434,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1540-694-CM26</t>
+          <t>1540-695-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14458,12 +14474,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -14477,13 +14493,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1605.62</v>
+        <v>1337.2</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1540-698-CM26</t>
+          <t>1540-694-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14523,12 +14539,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.116.604-2</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -14542,7 +14558,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>785.98</v>
+        <v>1605.62</v>
       </c>
     </row>
     <row r="228">
@@ -14609,7 +14625,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1057402-2988-CM26</t>
+          <t>1057402-3225-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14668,7 +14684,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4161.07</v>
+        <v>2080.53</v>
       </c>
     </row>
     <row r="230">
@@ -14722,7 +14738,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14735,7 +14755,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1057402-3225-CM26</t>
+          <t>1057402-2988-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14794,7 +14814,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2080.53</v>
+        <v>4161.07</v>
       </c>
     </row>
     <row r="232">
@@ -15048,7 +15068,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3130-5654-CM26</t>
+          <t>3130-5658-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15088,12 +15108,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -15103,13 +15123,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1342.49</v>
+        <v>935.38</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3130-5658-CM26</t>
+          <t>3130-5654-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15149,12 +15169,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -15164,7 +15184,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>935.38</v>
+        <v>1342.49</v>
       </c>
     </row>
     <row r="238">
@@ -15300,7 +15320,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1057402-3770-CM26</t>
+          <t>902977-10-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15320,17 +15340,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15340,22 +15360,26 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>4539.27</v>
+        <v>1446.37</v>
       </c>
     </row>
     <row r="241">
@@ -15426,7 +15450,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>902977-10-CM26</t>
+          <t>1057402-3770-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15446,17 +15470,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15466,32 +15490,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1446.37</v>
+        <v>4539.27</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1540-969-CM26</t>
+          <t>1237328-152-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15516,12 +15536,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15531,12 +15551,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -15550,13 +15570,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>6701.49</v>
+        <v>5765.71</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1540-970-CM26</t>
+          <t>1540-969-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15596,12 +15616,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -15615,13 +15635,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>806.62</v>
+        <v>6701.49</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1540-971-CM26</t>
+          <t>1540-970-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15661,28 +15681,32 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>894.71</v>
+        <v>806.62</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1540-972-CM26</t>
+          <t>1540-971-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15722,12 +15746,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15737,13 +15761,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>805.73</v>
+        <v>894.71</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1237328-152-CM26</t>
+          <t>1540-972-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15768,12 +15792,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15783,26 +15807,22 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5765.71</v>
+        <v>805.73</v>
       </c>
     </row>
     <row r="248">
@@ -15873,7 +15893,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3130-5754-CM26</t>
+          <t>1057402-4313-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15898,12 +15918,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15913,12 +15933,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -15932,13 +15952,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1869.87</v>
+        <v>857.86</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1057402-4313-CM26</t>
+          <t>3130-5754-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15963,12 +15983,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15978,12 +15998,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -15997,7 +16017,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>857.86</v>
+        <v>1869.87</v>
       </c>
     </row>
     <row r="251">
@@ -16368,7 +16388,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16633,7 +16657,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3130-5875-CM26</t>
+          <t>3130-5876-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16673,12 +16697,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16688,13 +16712,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>837.9400000000001</v>
+        <v>868.21</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3130-5876-CM26</t>
+          <t>3130-5875-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16734,12 +16758,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16749,7 +16773,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>868.21</v>
+        <v>837.9400000000001</v>
       </c>
     </row>
     <row r="263">
@@ -17251,7 +17275,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1057402-5351-CM26</t>
+          <t>1057402-5867-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17291,28 +17315,32 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1172.51</v>
+        <v>831.62</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1057402-5867-CM26</t>
+          <t>1057402-5351-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17352,32 +17380,28 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.209.836-9</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>831.62</v>
+        <v>1172.51</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1057402-5090-CM26</t>
+          <t>1057402-5243-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17417,12 +17441,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17432,13 +17456,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>819.46</v>
+        <v>895.45</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1057402-5243-CM26</t>
+          <t>1057402-5090-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17478,12 +17502,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17493,13 +17517,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>895.45</v>
+        <v>819.46</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1057402-6040-CM26</t>
+          <t>1057402-6043-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17539,32 +17563,28 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>59.106.780-k</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>862.27</v>
+        <v>841.1900000000001</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1057402-6041-CM26</t>
+          <t>1057402-6040-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17604,12 +17624,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -17623,13 +17643,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>956.48</v>
+        <v>862.27</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1057402-6043-CM26</t>
+          <t>1057402-6044-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17669,12 +17689,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17684,13 +17704,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>841.1900000000001</v>
+        <v>839.2</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1057402-6044-CM26</t>
+          <t>1237328-326-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17715,12 +17735,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17730,28 +17750,32 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr"/>
+          <t>77.910.467-2</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>839.2</v>
+        <v>1896.2</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1237328-326-CM26</t>
+          <t>1057402-6041-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17776,12 +17800,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17791,12 +17815,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -17810,7 +17834,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1896.2</v>
+        <v>956.48</v>
       </c>
     </row>
     <row r="280">
@@ -18068,7 +18092,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1057402-6211-CM26</t>
+          <t>3130-6060-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18093,12 +18117,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18108,12 +18132,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -18123,13 +18147,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4856.03</v>
+        <v>2029.04</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3130-6060-CM26</t>
+          <t>1057402-6211-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18154,12 +18178,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18169,12 +18193,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -18184,7 +18208,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2029.04</v>
+        <v>4856.03</v>
       </c>
     </row>
     <row r="286">
@@ -18251,7 +18275,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1057402-6384-CM26</t>
+          <t>1057402-6429-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18291,28 +18315,32 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1053.37</v>
+        <v>913.04</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1057402-6429-CM26</t>
+          <t>1057402-6430-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18352,12 +18380,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -18371,13 +18399,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>913.04</v>
+        <v>11694.9</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1057402-6430-CM26</t>
+          <t>1057402-6431-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18417,32 +18445,28 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>59.106.780-k</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>11694.9</v>
+        <v>6784.31</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1057402-6431-CM26</t>
+          <t>1057402-6432-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18482,12 +18506,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18497,13 +18521,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>6784.31</v>
+        <v>2503.59</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1057402-6432-CM26</t>
+          <t>1057402-6384-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18543,12 +18567,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18558,7 +18582,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2503.59</v>
+        <v>1053.37</v>
       </c>
     </row>
     <row r="292">
@@ -18934,7 +18958,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1057402-6791-CM26</t>
+          <t>874750-207-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18954,17 +18978,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18974,12 +18998,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18989,13 +19013,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>839.65</v>
+        <v>2193.54</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>874750-207-CM26</t>
+          <t>1057402-6791-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19015,17 +19039,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19035,12 +19059,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19050,7 +19074,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2193.54</v>
+        <v>839.65</v>
       </c>
     </row>
     <row r="300">
@@ -19304,7 +19328,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>874750-241-CM26</t>
+          <t>1057402-7326-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19324,17 +19348,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19344,12 +19368,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -19359,13 +19383,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2481.88</v>
+        <v>3478.37</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1057402-7326-CM26</t>
+          <t>874750-238-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19385,17 +19409,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19405,28 +19429,32 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3478.37</v>
+        <v>7281.84</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>874750-238-CM26</t>
+          <t>874750-241-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19466,26 +19494,22 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>7281.84</v>
+        <v>2481.88</v>
       </c>
     </row>
     <row r="307">
@@ -19726,7 +19750,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19926,7 +19954,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1540-1727-CM26</t>
+          <t>1540-1724-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19966,32 +19994,28 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>837.97</v>
+        <v>887.88</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1540-1729-CM26</t>
+          <t>1540-1725-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20031,28 +20055,32 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr"/>
+          <t>84.609.600-0</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>873.63</v>
+        <v>852.3</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1540-1725-CM26</t>
+          <t>1540-1726-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20092,28 +20120,32 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>852.3</v>
+        <v>854.01</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1540-1724-CM26</t>
+          <t>1540-1729-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20153,12 +20185,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -20168,13 +20200,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>887.88</v>
+        <v>873.63</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1540-1726-CM26</t>
+          <t>1540-1727-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20214,12 +20246,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -20233,7 +20265,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>854.01</v>
+        <v>837.97</v>
       </c>
     </row>
     <row r="319">
@@ -20670,7 +20702,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1057402-8930-CM26</t>
+          <t>1057402-8733-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20710,28 +20742,32 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1945.11</v>
+        <v>979.67</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1057402-8704-CM26</t>
+          <t>1057402-8930-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20771,28 +20807,32 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1325.78</v>
+        <v>1945.11</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1057402-8733-CM26</t>
+          <t>1057402-8704-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20832,26 +20872,22 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>59.106.780-k</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>979.67</v>
+        <v>1325.78</v>
       </c>
     </row>
     <row r="329">
@@ -20918,7 +20954,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1237328-485-CM26</t>
+          <t>1237328-486-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20958,12 +20994,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -20973,13 +21009,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2106.75</v>
+        <v>6771.13</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1237328-486-CM26</t>
+          <t>1237328-485-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21019,12 +21055,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -21034,7 +21070,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>6771.13</v>
+        <v>2106.75</v>
       </c>
     </row>
     <row r="332">
@@ -21170,7 +21206,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1057402-9247-CM26</t>
+          <t>1237328-496-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21190,17 +21226,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21210,32 +21246,28 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1965.28</v>
+        <v>8309.98</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>3130-6492-CM26</t>
+          <t>1237328-495-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21260,12 +21292,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21275,32 +21307,28 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.383.300-0</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2620.55</v>
+        <v>4226.99</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1237328-496-CM26</t>
+          <t>1057402-9115-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21320,17 +21348,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21340,12 +21368,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.209.836-9</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -21355,13 +21383,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>8309.98</v>
+        <v>1069.26</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>707427-47-CM26</t>
+          <t>3130-6492-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21381,17 +21409,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21401,28 +21429,32 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2210.42</v>
+        <v>2620.55</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1057402-9115-CM26</t>
+          <t>707427-47-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21442,17 +21474,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21462,12 +21494,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -21477,13 +21509,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1069.26</v>
+        <v>2210.42</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1057402-9084-CM26</t>
+          <t>1057402-9247-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21523,12 +21555,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -21542,13 +21574,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1327.91</v>
+        <v>1965.28</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1237328-495-CM26</t>
+          <t>1057402-9084-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21573,12 +21605,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21588,28 +21620,32 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>4226.99</v>
+        <v>1327.91</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3130-6546-CM26</t>
+          <t>3130-6547-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21629,7 +21665,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -21649,32 +21685,28 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>888.21</v>
+        <v>796.9400000000001</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>3130-6547-CM26</t>
+          <t>3130-6546-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21714,22 +21746,26 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>796.9400000000001</v>
+        <v>888.21</v>
       </c>
     </row>
     <row r="343">
@@ -21755,7 +21791,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -21816,7 +21852,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -21926,7 +21962,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1057402-9857-CM26</t>
+          <t>1540-2044-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21951,12 +21987,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21966,28 +22002,32 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>777.72</v>
+        <v>848.41</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1540-2044-CM26</t>
+          <t>1057402-9857-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22012,12 +22052,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22027,12 +22067,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -22042,13 +22082,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>848.41</v>
+        <v>777.72</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1057402-9917-CM26</t>
+          <t>1057402-9967-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22088,12 +22128,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>5.892.120-3</t>
+          <t>76.209.836-9</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -22103,13 +22143,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>753.03</v>
+        <v>1020.08</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1057402-9967-CM26</t>
+          <t>1057402-9917-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22149,12 +22189,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
+          <t>5.892.120-3</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -22164,7 +22204,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1020.08</v>
+        <v>753.03</v>
       </c>
     </row>
     <row r="350">
@@ -22190,7 +22230,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -22251,7 +22291,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -22292,7 +22332,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>3130-6642-CM26</t>
+          <t>3130-6643-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22312,7 +22352,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -22332,32 +22372,28 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.400-5</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2095.98</v>
+        <v>920.7</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>3130-6643-CM26</t>
+          <t>3130-6642-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22377,7 +22413,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -22397,28 +22433,32 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>920.7</v>
+        <v>2095.98</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1540-2104-CM26</t>
+          <t>1540-2109-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22438,7 +22478,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -22458,12 +22498,12 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -22473,13 +22513,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1740.25</v>
+        <v>775.83</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1540-2105-CM26</t>
+          <t>1540-2108-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22499,7 +22539,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -22538,13 +22578,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1036.57</v>
+        <v>746.0700000000001</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1540-2106-CM26</t>
+          <t>1540-2107-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22564,7 +22604,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -22584,28 +22624,32 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>760.52</v>
+        <v>2724.37</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1540-2107-CM26</t>
+          <t>1540-2106-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22625,7 +22669,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -22645,32 +22689,28 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>2724.37</v>
+        <v>760.52</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1540-2108-CM26</t>
+          <t>1540-2105-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22690,7 +22730,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -22729,13 +22769,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>746.0700000000001</v>
+        <v>1036.57</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1540-2109-CM26</t>
+          <t>1540-2111-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22755,7 +22795,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -22775,12 +22815,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -22790,7 +22830,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>775.83</v>
+        <v>748.04</v>
       </c>
     </row>
     <row r="360">
@@ -22816,7 +22856,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -22861,7 +22901,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1540-2111-CM26</t>
+          <t>1540-2104-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22881,7 +22921,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -22901,12 +22941,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K361" t="inlineStr"/>
@@ -22916,7 +22956,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>748.04</v>
+        <v>1740.25</v>
       </c>
     </row>
     <row r="362">
@@ -22942,7 +22982,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -22987,7 +23027,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1057402-9994-CM26</t>
+          <t>3130-6668-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23007,17 +23047,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23027,28 +23067,32 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1988.04</v>
+        <v>1925.45</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>3130-6668-CM26</t>
+          <t>1057402-9994-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23068,46 +23112,1221 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>1988.04</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1057402-10422-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>870.59</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>874750-346-CM26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>2005.23</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>874750-347-CM26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1057402-10940-CM26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>1153.59</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>3130-6745-CM26</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
         <is>
           <t>61.102.029-5</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr">
+      <c r="G369" t="inlineStr">
         <is>
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>919.35</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>3130-6750-CM26</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>77.237.150-0</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>862.45</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1239966-449-CM26</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>71.165.800-9</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="n">
+        <v>2085.06</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1057402-10803-CM26</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="n">
+        <v>11030.4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1057402-10838-CM26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>1499.83</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1057402-10848-CM26</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>COMERCIAL LBF LIMITADA</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M364" s="2" t="n">
-        <v>1925.45</v>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="n">
+        <v>3040.51</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2354-367-CM26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>DELTAMED LIMITADA</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>76.512.686-k</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>929.0599999999999</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>874750-375-CM26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>1996.34</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>874750-376-CM26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>794.53</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>3130-6779-CM26</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>1636.35</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1057402-10877-CM26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>76.209.836-9</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>992.5599999999999</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>874750-380-CM26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>2622.05</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1057402-11237-CM26</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>749.13</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>3130-6800-CM26</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>1523.72</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>3130-6803-CM26</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>1003.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M384"/>
+  <dimension ref="A1:M389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2079,7 +2079,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>874750-86-CM25</t>
+          <t>1057402-15322-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BARADENT SUR SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.701.829-0</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1458</v>
+        <v>4529.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>874750-85-CM25</t>
+          <t>874750-86-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2184,28 +2184,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>BARADENT SUR SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.701.829-0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1341.28</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057402-15322-CM25</t>
+          <t>3130-1509-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2230,12 +2234,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2245,12 +2249,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2264,13 +2268,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4529.17</v>
+        <v>1011.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3130-1509-CM25</t>
+          <t>874750-85-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2290,17 +2294,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2310,26 +2314,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.400-5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1011.86</v>
+        <v>1341.28</v>
       </c>
     </row>
     <row r="31">
@@ -2896,7 +2896,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2099-160-CM25</t>
+          <t>1057402-22171-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>695.02</v>
+        <v>4282.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057402-22171-CM25</t>
+          <t>2099-160-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4282.79</v>
+        <v>695.02</v>
       </c>
     </row>
     <row r="42">
@@ -3140,7 +3140,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>874750-131-CM25</t>
+          <t>1540-825-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3160,17 +3160,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1290.63</v>
+        <v>5216.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1540-825-CM25</t>
+          <t>874750-131-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5216.37</v>
+        <v>1290.63</v>
       </c>
     </row>
     <row r="46">
@@ -3571,7 +3571,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1540-922-CM25</t>
+          <t>1540-924-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CEGAMED CHILE S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>99.593.170-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1822.2</v>
+        <v>9533.75</v>
       </c>
     </row>
     <row r="52">
@@ -3697,7 +3697,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1540-924-CM25</t>
+          <t>1540-922-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CEGAMED CHILE S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>99.593.170-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9533.75</v>
+        <v>1822.2</v>
       </c>
     </row>
     <row r="54">
@@ -3884,7 +3884,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3130-1827-CM25</t>
+          <t>3130-1825-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3924,26 +3924,22 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>867.71</v>
+        <v>920.12</v>
       </c>
     </row>
     <row r="57">
@@ -4071,7 +4067,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3130-1825-CM25</t>
+          <t>3130-1827-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4111,22 +4107,26 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>920.12</v>
+        <v>867.71</v>
       </c>
     </row>
     <row r="60">
@@ -4258,7 +4258,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1237328-111-CM25</t>
+          <t>1237328-109-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4111.22</v>
+        <v>20316.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1237328-109-CM25</t>
+          <t>1237328-111-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>20316.96</v>
+        <v>4111.22</v>
       </c>
     </row>
     <row r="64">
@@ -5673,7 +5673,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3130-2372-CM25</t>
+          <t>3130-2364-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5732,13 +5732,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>735.33</v>
+        <v>3005.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3130-2364-CM25</t>
+          <t>3130-2365-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5778,32 +5778,28 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3005.65</v>
+        <v>1977.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3130-2365-CM25</t>
+          <t>3130-2367-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5843,22 +5839,26 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1977.89</v>
+        <v>1695.69</v>
       </c>
     </row>
     <row r="88">
@@ -5929,7 +5929,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3130-2370-CM25</t>
+          <t>3130-2372-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5969,28 +5969,32 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>77.910.467-2</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>716.6900000000001</v>
+        <v>735.33</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3130-2367-CM25</t>
+          <t>3130-2370-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6030,26 +6034,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.237.150-0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1695.69</v>
+        <v>716.6900000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6120,7 +6120,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1237328-223-CM25</t>
+          <t>1237328-221-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8461.57</v>
+        <v>750.6</v>
       </c>
     </row>
     <row r="93">
@@ -6242,7 +6242,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1237328-221-CM25</t>
+          <t>1237328-223-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>750.6</v>
+        <v>8461.57</v>
       </c>
     </row>
     <row r="95">
@@ -6990,7 +6990,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1540-1887-CM25</t>
+          <t>1540-1888-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7049,13 +7049,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1255.64</v>
+        <v>1351.1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1540-1888-CM25</t>
+          <t>1540-1887-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1351.1</v>
+        <v>1255.64</v>
       </c>
     </row>
     <row r="108">
@@ -7242,7 +7242,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1057402-27878-CM25</t>
+          <t>1237328-387-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>786.1</v>
+        <v>4851.18</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1237328-387-CM25</t>
+          <t>874750-376-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7343,28 +7343,32 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MAYORDENT DENTAL LIMITADA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>76.271.360-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4851.18</v>
+        <v>762.61</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1057402-27876-CM25</t>
+          <t>1057402-27878-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7419,13 +7423,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1023.72</v>
+        <v>786.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>874750-376-CM25</t>
+          <t>1057402-27876-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7445,17 +7449,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7465,26 +7469,22 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>MAYORDENT DENTAL LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.271.360-8</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>762.61</v>
+        <v>1023.72</v>
       </c>
     </row>
     <row r="114">
@@ -7551,7 +7551,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1237328-467-CM25</t>
+          <t>1237328-468-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7606,13 +7606,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1640.44</v>
+        <v>4842.1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1237328-468-CM25</t>
+          <t>1237328-467-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4842.1</v>
+        <v>1640.44</v>
       </c>
     </row>
     <row r="117">
@@ -7795,7 +7795,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1540-2126-CM25</t>
+          <t>1540-2123-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7835,32 +7835,28 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>974.87</v>
+        <v>4815.1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1540-2122-CM25</t>
+          <t>1540-2125-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7900,12 +7896,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7915,7 +7911,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>726.24</v>
+        <v>7562.31</v>
       </c>
     </row>
     <row r="121">
@@ -7982,7 +7978,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1540-2123-CM25</t>
+          <t>1540-2122-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8022,12 +8018,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -8037,7 +8033,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4815.1</v>
+        <v>726.24</v>
       </c>
     </row>
     <row r="123">
@@ -8104,7 +8100,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1540-2125-CM25</t>
+          <t>1540-2126-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8144,28 +8140,32 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>7562.31</v>
+        <v>974.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057402-32429-CM25</t>
+          <t>1057402-32418-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -8220,13 +8220,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>788.64</v>
+        <v>794.98</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1057402-32418-CM25</t>
+          <t>1057402-32429-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8281,13 +8281,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>794.98</v>
+        <v>788.64</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>902977-23-CM25</t>
+          <t>5147-287-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8327,28 +8327,32 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1049.44</v>
+        <v>4474.09</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>874750-418-CM25</t>
+          <t>902977-22-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8368,17 +8372,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8388,28 +8392,32 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1009.72</v>
+        <v>737.45</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>902977-24-CM25</t>
+          <t>902977-23-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8449,12 +8457,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8464,13 +8472,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>811.34</v>
+        <v>1049.44</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>902977-22-CM25</t>
+          <t>902977-24-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8510,32 +8518,28 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.581.120-6</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>737.45</v>
+        <v>811.34</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5147-287-CM25</t>
+          <t>874750-418-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8555,17 +8559,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8575,26 +8579,22 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.226.228-2</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4474.09</v>
+        <v>1009.72</v>
       </c>
     </row>
     <row r="132">
@@ -8722,7 +8722,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3130-2968-CM25</t>
+          <t>3130-2973-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1845.73</v>
+        <v>910.29</v>
       </c>
     </row>
     <row r="135">
@@ -8913,7 +8913,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3130-2973-CM25</t>
+          <t>3130-2968-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8968,13 +8968,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>910.29</v>
+        <v>1845.73</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3130-2969-CM25</t>
+          <t>874750-442-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8994,17 +8994,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -9029,13 +9029,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>743.8</v>
+        <v>1015.69</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>874750-445-CM25</t>
+          <t>3130-2969-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9090,13 +9090,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2085.23</v>
+        <v>743.8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>874750-442-CM25</t>
+          <t>874750-445-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -9151,13 +9151,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1015.69</v>
+        <v>2085.23</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>874750-453-CM25</t>
+          <t>3130-4031-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9212,13 +9212,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>727.74</v>
+        <v>2258.02</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3130-4029-CM25</t>
+          <t>874750-453-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>CEGASURGICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.705.621-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>765.4</v>
+        <v>727.74</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3130-4030-CM25</t>
+          <t>3130-4029-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9319,12 +9319,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CEGASURGICAL SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.705.621-4</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>789.3200000000001</v>
+        <v>765.4</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3130-4031-CM25</t>
+          <t>3130-4030-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9380,12 +9380,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2258.02</v>
+        <v>789.3200000000001</v>
       </c>
     </row>
     <row r="145">
@@ -9718,7 +9718,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3130-4150-CM25</t>
+          <t>1239966-440-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9738,17 +9738,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9773,13 +9773,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>955.3200000000001</v>
+        <v>914.23</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1239966-440-CM25</t>
+          <t>3130-4150-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9799,17 +9799,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>914.23</v>
+        <v>955.3200000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9966,7 +9966,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>874750-482-CM25</t>
+          <t>874750-483-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10006,12 +10006,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10025,13 +10025,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>904.67</v>
+        <v>747.55</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>874750-483-CM25</t>
+          <t>874750-482-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10071,12 +10071,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>747.55</v>
+        <v>904.67</v>
       </c>
     </row>
     <row r="156">
@@ -10462,7 +10462,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3130-4447-CM25</t>
+          <t>1237328-703-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10517,13 +10517,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2449.78</v>
+        <v>5510.8</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1237328-703-CM25</t>
+          <t>1237328-705-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>5510.8</v>
+        <v>5051.56</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1237328-705-CM25</t>
+          <t>1237328-704-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10639,13 +10639,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5051.56</v>
+        <v>1996.24</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1237328-704-CM25</t>
+          <t>3130-4447-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1996.24</v>
+        <v>2449.78</v>
       </c>
     </row>
     <row r="166">
@@ -10767,7 +10767,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1237328-718-CM25</t>
+          <t>1237328-713-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10807,28 +10807,32 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>77.910.467-2</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1855.99</v>
+        <v>1488.03</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1237328-713-CM25</t>
+          <t>1237328-718-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10848,7 +10852,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10868,32 +10872,28 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1488.03</v>
+        <v>1855.99</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3130-4486-CM25</t>
+          <t>1057402-43849-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>Pulsar Medical</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10948,13 +10948,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>788.1900000000001</v>
+        <v>1530.02</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1057402-43849-CM25</t>
+          <t>3130-4486-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Pulsar Medical</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1530.02</v>
+        <v>788.1900000000001</v>
       </c>
     </row>
     <row r="171">
@@ -11263,7 +11263,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057402-156-CM26</t>
+          <t>1057402-165-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11303,12 +11303,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11318,13 +11318,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2017.43</v>
+        <v>924.8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1057402-165-CM26</t>
+          <t>1057402-156-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11379,13 +11379,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>924.8</v>
+        <v>2017.43</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1057402-286-CM26</t>
+          <t>1057402-242-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11425,12 +11425,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>Pulsar Medical</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11440,13 +11440,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>908.26</v>
+        <v>1834.19</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1057402-242-CM26</t>
+          <t>1057402-286-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11486,12 +11486,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Pulsar Medical</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1834.19</v>
+        <v>908.26</v>
       </c>
     </row>
     <row r="179">
@@ -12182,7 +12182,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>874750-27-CM26</t>
+          <t>1057402-1177-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12202,17 +12202,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -12241,13 +12241,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>905.4400000000001</v>
+        <v>891.08</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1057402-1177-CM26</t>
+          <t>3130-5281-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12287,32 +12287,28 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.400-5</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>891.08</v>
+        <v>1423.79</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3130-5281-CM26</t>
+          <t>874750-27-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12332,17 +12328,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12352,28 +12348,32 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1423.79</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1057402-1110-CM26</t>
+          <t>1057402-1023-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12413,12 +12413,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12428,13 +12428,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>923.76</v>
+        <v>843.3099999999999</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1057402-1023-CM26</t>
+          <t>1057402-1110-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12489,7 +12489,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>843.3099999999999</v>
+        <v>923.76</v>
       </c>
     </row>
     <row r="195">
@@ -13304,7 +13304,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1057402-2304-CM26</t>
+          <t>3130-5423-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13344,26 +13344,22 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.054.237-7</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>829.09</v>
+        <v>1052.94</v>
       </c>
     </row>
     <row r="209">
@@ -13434,7 +13430,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3130-5423-CM26</t>
+          <t>1057402-2304-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13459,12 +13455,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13474,22 +13470,26 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1052.94</v>
+        <v>829.09</v>
       </c>
     </row>
     <row r="211">
@@ -13812,7 +13812,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>874750-81-CM26</t>
+          <t>874750-80-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>6731.23</v>
+        <v>1348.55</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>874750-80-CM26</t>
+          <t>874750-81-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1348.55</v>
+        <v>6731.23</v>
       </c>
     </row>
     <row r="218">
@@ -14125,7 +14125,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>855-35-CM26</t>
+          <t>1057402-2470-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14150,12 +14150,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14180,13 +14180,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4223.46</v>
+        <v>3295.21</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1057402-2470-CM26</t>
+          <t>855-35-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14211,12 +14211,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3295.21</v>
+        <v>4223.46</v>
       </c>
     </row>
     <row r="223">
@@ -14373,7 +14373,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1540-698-CM26</t>
+          <t>1540-695-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14413,12 +14413,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -14432,13 +14432,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>785.98</v>
+        <v>1337.2</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1540-697-CM26</t>
+          <t>1540-694-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14478,28 +14478,32 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>890.17</v>
+        <v>1605.62</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1540-695-CM26</t>
+          <t>1540-698-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14539,12 +14543,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -14558,13 +14562,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1337.2</v>
+        <v>785.98</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1540-694-CM26</t>
+          <t>1540-697-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14604,26 +14608,22 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1605.62</v>
+        <v>890.17</v>
       </c>
     </row>
     <row r="229">
@@ -14690,7 +14690,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1057402-3225-CM26</t>
+          <t>1057402-2988-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2080.53</v>
+        <v>4161.07</v>
       </c>
     </row>
     <row r="231">
@@ -14820,7 +14820,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1057402-2988-CM26</t>
+          <t>1057402-3225-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>4161.07</v>
+        <v>2080.53</v>
       </c>
     </row>
     <row r="233">
@@ -15385,7 +15385,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>902977-10-CM26</t>
+          <t>1057402-3770-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15405,17 +15405,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15425,26 +15425,22 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1446.37</v>
+        <v>4539.27</v>
       </c>
     </row>
     <row r="242">
@@ -15515,7 +15511,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1057402-3770-CM26</t>
+          <t>902977-10-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15535,17 +15531,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15555,28 +15551,32 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4539.27</v>
+        <v>1446.37</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1237328-152-CM26</t>
+          <t>1540-969-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15601,12 +15601,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15616,12 +15616,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>5765.71</v>
+        <v>6701.49</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1540-969-CM26</t>
+          <t>1540-970-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15681,12 +15681,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -15700,13 +15700,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>6701.49</v>
+        <v>806.62</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1540-970-CM26</t>
+          <t>1540-971-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15746,32 +15746,28 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>806.62</v>
+        <v>894.71</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1540-971-CM26</t>
+          <t>1540-972-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15811,12 +15807,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15826,13 +15822,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>894.71</v>
+        <v>805.73</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1540-972-CM26</t>
+          <t>1237328-152-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15857,12 +15853,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15872,22 +15868,26 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>805.73</v>
+        <v>5765.71</v>
       </c>
     </row>
     <row r="249">
@@ -15958,7 +15958,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1057402-4313-CM26</t>
+          <t>3130-5754-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15983,12 +15983,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -16017,13 +16017,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>857.86</v>
+        <v>1869.87</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3130-5754-CM26</t>
+          <t>1057402-4313-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -16082,7 +16082,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1869.87</v>
+        <v>857.86</v>
       </c>
     </row>
     <row r="252">
@@ -16214,7 +16214,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1057402-4516-CM26</t>
+          <t>3130-5797-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>4328.42</v>
+        <v>1781.71</v>
       </c>
     </row>
     <row r="255">
@@ -16344,7 +16344,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1057402-4519-CM26</t>
+          <t>1057402-4516-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16384,28 +16384,32 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>840.9400000000001</v>
+        <v>4328.42</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>3130-5797-CM26</t>
+          <t>1057402-4519-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16430,12 +16434,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16445,32 +16449,28 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1781.71</v>
+        <v>840.9400000000001</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1057402-4792-CM26</t>
+          <t>1057402-4735-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16510,32 +16510,28 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>59.077.290-9</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>11148.22</v>
+        <v>2301.33</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1057402-4735-CM26</t>
+          <t>1057402-4790-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16575,28 +16571,32 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2301.33</v>
+        <v>1858.04</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1057402-4790-CM26</t>
+          <t>1057402-4792-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16655,7 +16655,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1858.04</v>
+        <v>11148.22</v>
       </c>
     </row>
     <row r="261">
@@ -16722,7 +16722,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3130-5876-CM26</t>
+          <t>3130-5875-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16762,12 +16762,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16777,13 +16777,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>868.21</v>
+        <v>837.9400000000001</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3130-5875-CM26</t>
+          <t>3130-5876-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16823,12 +16823,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>837.9400000000001</v>
+        <v>868.21</v>
       </c>
     </row>
     <row r="264">
@@ -17153,7 +17153,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1057402-5535-CM26</t>
+          <t>1057402-5538-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17193,28 +17193,32 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1161.44</v>
+        <v>828.39</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1057402-5538-CM26</t>
+          <t>1057402-5535-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17254,26 +17258,22 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>59.077.290-9</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>828.39</v>
+        <v>1161.44</v>
       </c>
     </row>
     <row r="271">
@@ -17340,7 +17340,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1057402-5867-CM26</t>
+          <t>1057402-5090-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17380,32 +17380,28 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>59.077.290-9</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>831.62</v>
+        <v>819.46</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1057402-5351-CM26</t>
+          <t>1057402-5243-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17445,12 +17441,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17460,13 +17456,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1172.51</v>
+        <v>895.45</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1057402-5243-CM26</t>
+          <t>1057402-5351-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17506,12 +17502,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.209.836-9</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17521,13 +17517,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>895.45</v>
+        <v>1172.51</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1057402-5090-CM26</t>
+          <t>1057402-5867-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17567,28 +17563,32 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>819.46</v>
+        <v>831.62</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1057402-6043-CM26</t>
+          <t>1057402-6040-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17628,28 +17628,32 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>841.1900000000001</v>
+        <v>862.27</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1057402-6040-CM26</t>
+          <t>1057402-6041-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17689,12 +17693,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -17708,13 +17712,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>862.27</v>
+        <v>956.48</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1057402-6044-CM26</t>
+          <t>1057402-6043-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17754,12 +17758,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -17769,13 +17773,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>839.2</v>
+        <v>841.1900000000001</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1237328-326-CM26</t>
+          <t>1057402-6044-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17800,12 +17804,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17815,32 +17819,28 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1896.2</v>
+        <v>839.2</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1057402-6041-CM26</t>
+          <t>1237328-326-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17880,12 +17880,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.910.467-2</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -17899,7 +17899,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>956.48</v>
+        <v>1896.2</v>
       </c>
     </row>
     <row r="281">
@@ -18096,7 +18096,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2354-188-CM26</t>
+          <t>3130-6060-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18121,12 +18121,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18136,12 +18136,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -18151,13 +18151,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>829.91</v>
+        <v>2029.04</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3130-6060-CM26</t>
+          <t>1057402-6211-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18197,12 +18197,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA BBC CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -18212,13 +18212,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2029.04</v>
+        <v>4856.03</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1057402-6211-CM26</t>
+          <t>2354-188-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18243,12 +18243,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18258,12 +18258,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -18273,7 +18273,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>4856.03</v>
+        <v>829.91</v>
       </c>
     </row>
     <row r="287">
@@ -19023,7 +19023,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>874750-207-CM26</t>
+          <t>1057402-6791-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19043,17 +19043,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19078,13 +19078,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2193.54</v>
+        <v>839.65</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1057402-6791-CM26</t>
+          <t>874750-207-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19104,17 +19104,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19124,12 +19124,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -19139,7 +19139,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>839.65</v>
+        <v>2193.54</v>
       </c>
     </row>
     <row r="301">
@@ -19954,7 +19954,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1540-1728-CM26</t>
+          <t>1540-1724-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19994,32 +19994,28 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2660.12</v>
+        <v>887.88</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1540-1724-CM26</t>
+          <t>1540-1727-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20059,28 +20055,32 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>887.88</v>
+        <v>837.97</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1540-1725-CM26</t>
+          <t>1540-1728-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20120,12 +20120,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -20139,13 +20139,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>852.3</v>
+        <v>2660.12</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1540-1726-CM26</t>
+          <t>1540-1729-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20185,32 +20185,28 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>854.01</v>
+        <v>873.63</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1540-1729-CM26</t>
+          <t>1540-1725-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20250,28 +20246,32 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr"/>
+          <t>84.609.600-0</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>873.63</v>
+        <v>852.3</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1540-1727-CM26</t>
+          <t>1540-1726-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20311,12 +20311,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -20330,7 +20330,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>837.97</v>
+        <v>854.01</v>
       </c>
     </row>
     <row r="320">
@@ -20767,7 +20767,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1057402-8733-CM26</t>
+          <t>1057402-8704-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20807,32 +20807,28 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>59.106.780-k</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>979.67</v>
+        <v>1325.78</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1057402-8930-CM26</t>
+          <t>1057402-8733-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20872,12 +20868,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -20891,13 +20887,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1945.11</v>
+        <v>979.67</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1057402-8704-CM26</t>
+          <t>1057402-8930-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20937,22 +20933,26 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1325.78</v>
+        <v>1945.11</v>
       </c>
     </row>
     <row r="330">
@@ -21019,7 +21019,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1237328-486-CM26</t>
+          <t>1237328-485-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21059,12 +21059,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -21074,13 +21074,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>6771.13</v>
+        <v>2106.75</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1237328-485-CM26</t>
+          <t>1237328-486-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21120,12 +21120,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -21135,7 +21135,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2106.75</v>
+        <v>6771.13</v>
       </c>
     </row>
     <row r="333">
@@ -21271,7 +21271,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1237328-496-CM26</t>
+          <t>1057402-9084-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21291,17 +21291,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21311,28 +21311,32 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>8309.98</v>
+        <v>1327.91</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1237328-495-CM26</t>
+          <t>1057402-9115-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21357,12 +21361,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21372,12 +21376,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>76.209.836-9</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -21387,13 +21391,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>4226.99</v>
+        <v>1069.26</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1057402-9115-CM26</t>
+          <t>1237328-495-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21418,12 +21422,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21433,12 +21437,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K337" t="inlineStr"/>
@@ -21448,13 +21452,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1069.26</v>
+        <v>4226.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>3130-6492-CM26</t>
+          <t>707427-47-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21474,17 +21478,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21494,32 +21498,28 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>2620.55</v>
+        <v>2210.42</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>707427-47-CM26</t>
+          <t>1237328-496-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21544,12 +21544,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21559,12 +21559,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K339" t="inlineStr"/>
@@ -21574,13 +21574,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2210.42</v>
+        <v>8309.98</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1057402-9247-CM26</t>
+          <t>3130-6492-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21605,12 +21605,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21639,13 +21639,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1965.28</v>
+        <v>2620.55</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1057402-9084-CM26</t>
+          <t>1057402-9247-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21685,12 +21685,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -21704,13 +21704,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1327.91</v>
+        <v>1965.28</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>3130-6547-CM26</t>
+          <t>3130-6546-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21750,28 +21750,32 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>796.9400000000001</v>
+        <v>888.21</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>3130-6546-CM26</t>
+          <t>3130-6547-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21811,26 +21815,22 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>888.21</v>
+        <v>796.9400000000001</v>
       </c>
     </row>
     <row r="344">
@@ -22027,7 +22027,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1540-2044-CM26</t>
+          <t>1057402-9857-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22052,12 +22052,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22067,32 +22067,28 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>848.41</v>
+        <v>777.72</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1057402-9857-CM26</t>
+          <t>1540-2044-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22117,12 +22113,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22132,28 +22128,32 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>777.72</v>
+        <v>848.41</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1057402-9967-CM26</t>
+          <t>1057402-9917-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22193,12 +22193,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
+          <t>5.892.120-3</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -22208,13 +22208,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1020.08</v>
+        <v>753.03</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1057402-9917-CM26</t>
+          <t>1057402-9967-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22254,12 +22254,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>5.892.120-3</t>
+          <t>76.209.836-9</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -22269,13 +22269,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>753.03</v>
+        <v>1020.08</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>3130-6620-CM26</t>
+          <t>1057402-10030-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22300,12 +22300,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>Pulsar Medical</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -22330,13 +22330,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>928.36</v>
+        <v>790.42</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1057402-10030-CM26</t>
+          <t>3130-6620-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22361,12 +22361,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22376,12 +22376,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Pulsar Medical</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K352" t="inlineStr"/>
@@ -22391,13 +22391,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>790.42</v>
+        <v>928.36</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>3130-6643-CM26</t>
+          <t>3130-6642-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22437,28 +22437,32 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>920.7</v>
+        <v>2095.98</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>3130-6642-CM26</t>
+          <t>3130-6643-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22498,32 +22502,28 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.400-5</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>2095.98</v>
+        <v>920.7</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1540-2109-CM26</t>
+          <t>1540-2104-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22563,12 +22563,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -22578,13 +22578,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>775.83</v>
+        <v>1740.25</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1540-2108-CM26</t>
+          <t>1540-2105-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22643,13 +22643,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>746.0700000000001</v>
+        <v>1036.57</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1540-2107-CM26</t>
+          <t>1540-2106-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22689,32 +22689,28 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>2724.37</v>
+        <v>760.52</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1540-2106-CM26</t>
+          <t>1540-2107-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22754,28 +22750,32 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>760.52</v>
+        <v>2724.37</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1540-2105-CM26</t>
+          <t>1540-2108-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22834,13 +22834,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1036.57</v>
+        <v>746.0700000000001</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1540-2111-CM26</t>
+          <t>1540-2109-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22880,12 +22880,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22895,13 +22895,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>748.04</v>
+        <v>775.83</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1540-2110-CM26</t>
+          <t>1540-2111-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22941,32 +22941,28 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.581.120-6</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>4343.7</v>
+        <v>748.04</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1540-2104-CM26</t>
+          <t>1540-2110-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23006,22 +23002,26 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1740.25</v>
+        <v>4343.7</v>
       </c>
     </row>
     <row r="363">
@@ -23840,7 +23840,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2354-367-CM26</t>
+          <t>1057402-10877-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -23865,12 +23865,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>76.209.836-9</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -23895,7 +23895,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>929.0599999999999</v>
+        <v>992.5599999999999</v>
       </c>
     </row>
     <row r="377">
@@ -24092,7 +24092,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1057402-10877-CM26</t>
+          <t>2354-367-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24117,12 +24117,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -24132,12 +24132,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>ARTICULOS MEDICOS Y QUIRURGICOS CHILE S.A.</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K380" t="inlineStr"/>
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>992.5599999999999</v>
+        <v>929.0599999999999</v>
       </c>
     </row>
     <row r="381">
@@ -24392,6 +24392,311 @@
       </c>
       <c r="M384" s="2" t="n">
         <v>1003.55</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>3130-6804-CM26</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Pulsar Medical</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>76.923.737-2</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>1898.95</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>1237328-711-CM26</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>1021.36</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>1057402-11235-CM26</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>59.106.780-k</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>1818.61</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>1237328-709-CM26</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>22887.73</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1237328-710-CM26</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>MEDIPLEX S A</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>86.383.300-0</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="n">
+        <v>3349.84</v>
       </c>
     </row>
   </sheetData>
